--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0180.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0180.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Măng cụt không phải quả bản địa của Kim Châu. Chúng thường được nhập khẩu bằng đường biển. Tớ nghĩ chúng ta có thể tìm thấy nhiều măng cụt hơn ở các khu chợ gần đây.</t>
+          <t>Măng cụt không phải quả bản địa của Jinzhou. Chúng thường được nhập khẩu bằng đường biển. Tớ nghĩ chúng ta có thể tìm thấy nhiều măng cụt hơn ở các khu chợ gần đây.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Nói đến kẹo, chẳng ai hiểu chúng bằng lũ trẻ ở Kim Châu cả!</t>
+          <t>Nói đến kẹo, chẳng ai hiểu chúng bằng lũ trẻ ở Jinzhou cả!</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Cậu muốn gì với cái đó?</t>
+          <t>Mày muốn gì với cái đó?</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Ừ, chính là cái "bầu" đeo ở thắt lưng cậu ấy. Thiết bị mà mọi Cộng Hưởng Giả đều mang theo.</t>
+          <t>Ừ, chính là cái "bầu" đeo ở thắt lưng cậu ấy. Thiết bị mà mọi Resonator đều mang theo.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Họ đâu có bảo ta không được!</t>
+          <t>Họ đâu có bảo tao không được!</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Ta được gặp... Quý cô Sanhua! Cô ấy còn quay lại nhìn ta nữa chứ!</t>
+          <t>Tao được gặp... Quý cô Sanhua! Cô ấy còn quay lại nhìn tao nữa chứ!</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vậy đây chính là sự tự tin thực sự của một Rover chúng ta!</t>
+          <t>Vậy đây chính là sự tự tin thực sự của một Vận Mệnh Giả chúng ta!</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Ta cũng đồng ý. Cho đến giờ, cậu đã đáp ứng đủ mọi tiêu chí trong mô tả của Quan Phán.</t>
+          <t>Tao cũng đồng ý. Cho đến giờ, cậu đã đáp ứng đủ mọi tiêu chí trong mô tả của Quan Phán.</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Trừ khi cô ấy đang đi công tác, hoặc... khi an nguy của Kim Châu bị đe dọa.</t>
+          <t>Trừ khi cô ấy đang đi công tác, hoặc... khi an nguy của Jinzhou bị đe dọa.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Có điều gì đó trong đầu rồi phải không, Rover?</t>
+          <t>Có điều gì đó trong đầu rồi phải không, Vận Mệnh Giả?</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Ta không theo kịp mạch suy nghĩ của cậu lắm, nhưng gặp mặt Quan tòa cũng chẳng hại gì.</t>
+          <t>Tao không theo kịp mạch suy nghĩ của cậu lắm, nhưng gặp mặt Quan tòa cũng chẳng hại gì.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Nghe có chút quen quen... Dù sao,既然 Đội Trưởng đã nói, tôi phải nghe theo thôi.</t>
+          <t>Nghe có chút quen quen... Dù sao, vì Đội Trưởng đã nói, tôi phải nghe theo thôi.</t>
         </is>
       </c>
     </row>
